--- a/Python_Code/src/XGBOOST_sequia/dataset_salida/importancia_variables_xgboost.xlsx
+++ b/Python_Code/src/XGBOOST_sequia/dataset_salida/importancia_variables_xgboost.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>f36</t>
+          <t>f35</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40.81068420410156</v>
+        <v>43.3473014831543</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>f31</t>
+          <t>f30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.823641777038574</v>
+        <v>10.13828372955322</v>
       </c>
     </row>
     <row r="4">
@@ -483,212 +483,212 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>bio19</t>
+          <t>bio2</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.465034961700439</v>
+        <v>7.689760208129883</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>f39</t>
+          <t>f37</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bio2</t>
+          <t>bio19</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7.349905014038086</v>
+        <v>7.661849975585938</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>f51</t>
+          <t>f31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>srad_10</t>
+          <t>bio10</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.754047870635986</v>
+        <v>6.076294422149658</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>f13</t>
+          <t>f50</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AWCtS_M_sl1</t>
+          <t>srad_10</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.220449924468994</v>
+        <v>5.881461620330811</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>f8</t>
+          <t>f12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MODCF_meanannual</t>
+          <t>AWCtS_M_sl1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.192896366119385</v>
+        <v>5.512382984161377</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>f23</t>
+          <t>f7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHIHOX_M_sl1</t>
+          <t>MODCF_meanannual</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.055070400238037</v>
+        <v>4.373530864715576</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>f46</t>
+          <t>f22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>prec_4</t>
+          <t>PHIHOX_M_sl1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.931113958358765</v>
+        <v>3.910871744155884</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f10</t>
+          <t>f45</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>current_30arcsec_continentality</t>
+          <t>prec_4</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3.666910648345947</v>
+        <v>3.567928075790405</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>f42</t>
+          <t>f49</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>bio9</t>
+          <t>srad_1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3.516492605209351</v>
+        <v>3.470458030700684</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>f40</t>
+          <t>f9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>bio3</t>
+          <t>current_30arcsec_continentality</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.46167778968811</v>
+        <v>3.376127958297729</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>f2</t>
+          <t>f56</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORIGCTY</t>
+          <t>wind_10</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3.231077194213867</v>
+        <v>2.995563745498657</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>f14</t>
+          <t>f41</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CECSOL_M_sl1</t>
+          <t>bio9</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3.148500204086304</v>
+        <v>2.955661535263062</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>f32</t>
+          <t>f43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bio10</t>
+          <t>prec_10</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.101860523223877</v>
+        <v>2.896206855773926</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>f55</t>
+          <t>f53</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>srad_9</t>
+          <t>srad_5</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3.032739400863647</v>
+        <v>2.887679100036621</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>f24</t>
+          <t>f23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -697,358 +697,358 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.956659317016602</v>
+        <v>2.838414192199707</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>f57</t>
+          <t>f51</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>wind_10</t>
+          <t>srad_3</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.880497217178345</v>
+        <v>2.820540428161621</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>f52</t>
+          <t>f39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>srad_3</t>
+          <t>bio3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.784198045730591</v>
+        <v>2.794052362442017</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>f54</t>
+          <t>f13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>srad_5</t>
+          <t>CECSOL_M_sl1</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.772122383117676</v>
+        <v>2.679937362670898</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>f44</t>
+          <t>f26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>prec_10</t>
+          <t>SLTPPT_M_sl1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.747365474700928</v>
+        <v>2.591610670089722</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>f50</t>
+          <t>f29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>srad_1</t>
+          <t>ACDWRB_M_ss</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.63495397567749</v>
+        <v>2.582760334014893</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>f27</t>
+          <t>f52</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SLTPPT_M_sl1</t>
+          <t>srad_4</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.484419107437134</v>
+        <v>2.539535999298096</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>f35</t>
+          <t>f33</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>bio14</t>
+          <t>bio13</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.416043996810913</v>
+        <v>2.533365249633789</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>f7</t>
+          <t>f55</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MODCF_CloudForestPrediction</t>
+          <t>wind_1</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.30810022354126</v>
+        <v>2.529285669326782</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>f41</t>
+          <t>f6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bio8</t>
+          <t>MODCF_CloudForestPrediction</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.288448333740234</v>
+        <v>2.343192100524902</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>f30</t>
+          <t>f40</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ACDWRB_M_ss</t>
+          <t>bio8</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.282368183135986</v>
+        <v>2.260411500930786</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>f37</t>
+          <t>f54</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>bio18</t>
+          <t>srad_9</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2.261186599731445</v>
+        <v>2.240015983581543</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>f18</t>
+          <t>f4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BDRICM_M</t>
+          <t>ELEVATION</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2.225297451019287</v>
+        <v>2.228330850601196</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>f34</t>
+          <t>f24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>bio13</t>
+          <t>BDRLOG_M</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2.223660230636597</v>
+        <v>2.2011399269104</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>f56</t>
+          <t>f44</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wind_1</t>
+          <t>prec_11</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.105665683746338</v>
+        <v>2.160050630569458</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>f9</t>
+          <t>f20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MODCF_seasonality_concentration</t>
+          <t>OCDENS_M_sl1</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.00645637512207</v>
+        <v>2.146564722061157</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>f45</t>
+          <t>f46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>prec_11</t>
+          <t>prec_5</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1.930838704109192</v>
+        <v>2.129639387130737</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>f47</t>
+          <t>f36</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>prec_5</t>
+          <t>bio18</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.870600342750549</v>
+        <v>1.932073473930359</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>f53</t>
+          <t>f17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>srad_4</t>
+          <t>BDRICM_M</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.8375084400177</v>
+        <v>1.817403197288513</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>f16</t>
+          <t>f34</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CLYPPT_M_sl1</t>
+          <t>bio14</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.821795105934143</v>
+        <v>1.69485867023468</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>f21</t>
+          <t>f8</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OCDENS_M_sl1</t>
+          <t>MODCF_seasonality_concentration</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1.795262336730957</v>
+        <v>1.630917906761169</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>f25</t>
+          <t>f15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BDRLOG_M</t>
+          <t>CLYPPT_M_sl1</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.788193345069885</v>
+        <v>1.571151256561279</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>f4</t>
+          <t>f47</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SAMPSTAT</t>
+          <t>prec_6</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1.538395524024963</v>
+        <v>1.51545774936676</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>f29</t>
+          <t>f11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WWP_M_sl1</t>
+          <t>AWCh1_M_sl2</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1.530466437339783</v>
+        <v>1.506476640701294</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>f49</t>
+          <t>f48</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1057,193 +1057,193 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.479490876197815</v>
+        <v>1.4349604845047</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>f33</t>
+          <t>f28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bio12</t>
+          <t>WWP_M_sl1</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1.419347286224365</v>
+        <v>1.356413245201111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>f17</t>
+          <t>f3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CRFVOL_M_sl1</t>
+          <t>SAMPSTAT</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1.390285849571228</v>
+        <v>1.346772909164429</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>f15</t>
+          <t>f25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CECSOL_M_sl2</t>
+          <t>SNDPPT_M_sl1</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1.323847770690918</v>
+        <v>1.327030539512634</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>f19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ELEVATION</t>
+          <t>ORCDRC_M_sl2</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1.295013904571533</v>
+        <v>1.287928819656372</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>f48</t>
+          <t>f14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>prec_6</t>
+          <t>CECSOL_M_sl2</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1.283748507499695</v>
+        <v>1.219554662704468</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>f20</t>
+          <t>f32</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ORCDRC_M_sl2</t>
+          <t>bio12</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1.144217252731323</v>
+        <v>1.186402201652527</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>f11</t>
+          <t>f42</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AWCh1_M_sl1</t>
+          <t>prec_1</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1.086871743202209</v>
+        <v>1.058513402938843</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>f19</t>
+          <t>f2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ORCDRC_M_sl1</t>
+          <t>COLLSITE</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1.08160126209259</v>
+        <v>0.9703096151351929</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>f12</t>
+          <t>f16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AWCh1_M_sl2</t>
+          <t>CRFVOL_M_sl1</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1.076149702072144</v>
+        <v>0.9483612179756165</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>f43</t>
+          <t>f18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>prec_1</t>
+          <t>ORCDRC_M_sl1</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1.070508360862732</v>
+        <v>0.9315723776817322</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>f26</t>
+          <t>f21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SNDPPT_M_sl1</t>
+          <t>OCSTHA_M_sd1</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1.011033773422241</v>
+        <v>0.8604544401168823</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>f3</t>
+          <t>f10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>COLLSITE</t>
+          <t>AWCh1_M_sl1</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.9512608051300049</v>
+        <v>0.7044430375099182</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>f6</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1252,22 +1252,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.9119390845298767</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>f22</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>OCSTHA_M_sd1</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>0.8707355260848999</v>
+        <v>0.5747285485267639</v>
       </c>
     </row>
   </sheetData>
